--- a/branches/feature-careteam/CodeSystem-typ-av-fast-kontakt-cs.xlsx
+++ b/branches/feature-careteam/CodeSystem-typ-av-fast-kontakt-cs.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:03:46+00:00</t>
+    <t>2026-09-02T08:14:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/CodeSystem-typ-av-fast-kontakt-cs.xlsx
+++ b/branches/feature-careteam/CodeSystem-typ-av-fast-kontakt-cs.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T08:14:00+00:00</t>
+    <t>2026-09-08T07:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/CodeSystem-typ-av-fast-kontakt-cs.xlsx
+++ b/branches/feature-careteam/CodeSystem-typ-av-fast-kontakt-cs.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T07:27:40+00:00</t>
+    <t>2026-09-08T07:52:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/CodeSystem-typ-av-fast-kontakt-cs.xlsx
+++ b/branches/feature-careteam/CodeSystem-typ-av-fast-kontakt-cs.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T07:52:55+00:00</t>
+    <t>2026-09-11T06:20:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/CodeSystem-typ-av-fast-kontakt-cs.xlsx
+++ b/branches/feature-careteam/CodeSystem-typ-av-fast-kontakt-cs.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T06:20:50+00:00</t>
+    <t>2026-09-11T06:27:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/CodeSystem-typ-av-fast-kontakt-cs.xlsx
+++ b/branches/feature-careteam/CodeSystem-typ-av-fast-kontakt-cs.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T06:27:48+00:00</t>
+    <t>2026-09-11T07:06:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
